--- a/NEV公告车型行业分析_数据底表.xlsx
+++ b/NEV公告车型行业分析_数据底表.xlsx
@@ -529,7 +529,7 @@
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>生成日期 2026-09-27 · 权威源 NEV公告参数汇总表_合并版（341~410批）.xlsx</t>
+          <t>生成日期 2026-09-30 · 权威源 NEV公告参数汇总表_合并版（341~410批）.xlsx</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
         <v>64.58</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>33.71</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="9">
@@ -1051,10 +1051,10 @@
         <v>106</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>89</v>
@@ -7659,7 +7659,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>0.863</v>
+        <v>0.864</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>0.368</v>
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.863</v>
+        <v>0.864</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>1</v>
@@ -8139,10 +8139,10 @@
         <v>5.7</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>40.9</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="6">
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>33.08</v>
+        <v>33.07</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>32.7</v>
@@ -8808,7 +8808,7 @@
         <v>160.8</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>33.71</v>
+        <v>33.67</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>183.88</v>

--- a/NEV公告车型行业分析_数据底表.xlsx
+++ b/NEV公告车型行业分析_数据底表.xlsx
@@ -612,7 +612,7 @@
         <v>2023</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>64.48</v>
+        <v>64.53</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>26.38</v>
@@ -807,10 +807,10 @@
         <v>98</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8">
@@ -2860,7 +2860,7 @@
         <v>2023</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>12.5</v>
@@ -6892,13 +6892,13 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>95.40000000000001</v>
+        <v>100.4</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>99.8</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4.7</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="10">
@@ -7262,16 +7262,16 @@
         <v>1</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.544</v>
+        <v>0.545</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>0.922</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.696</v>
+        <v>0.697</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.677</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="6">
@@ -7284,7 +7284,7 @@
         <v>0.576</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.544</v>
+        <v>0.545</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>1</v>
@@ -7334,7 +7334,7 @@
         <v>0.619</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0.696</v>
+        <v>0.697</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>0.344</v>
@@ -7359,7 +7359,7 @@
         <v>0.347</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.677</v>
+        <v>0.678</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>0.295</v>
@@ -7937,10 +7937,10 @@
         <v>11.1</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>-6.7</v>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>63.91</v>
+        <v>63.92</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>64.2</v>
@@ -8723,7 +8723,7 @@
         <v>489.54</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>64.48</v>
+        <v>64.53</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>204.7</v>
@@ -8732,7 +8732,7 @@
         <v>1862.6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>116.72</v>

--- a/NEV公告车型行业分析_数据底表.xlsx
+++ b/NEV公告车型行业分析_数据底表.xlsx
@@ -52,6 +52,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关键指标汇总-BEV" sheetId="43" state="visible" r:id="rId43"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关键指标汇总-PHEV" sheetId="44" state="visible" r:id="rId44"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年度综合指标" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月销量分析" sheetId="46" state="visible" r:id="rId46"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2215,7 +2216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2688,6 +2689,16 @@
       <c r="B48" s="5" t="inlineStr">
         <is>
           <t>年度综合指标</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>月销量分析</t>
         </is>
       </c>
     </row>
@@ -8860,6 +8871,418 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>月销量参考（易车零售 · 2026-08 · 车系级数值）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>按通用名称聚合取最大值（同系多行共享车系级销量）；806 行有值中的 Top20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>排名</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>车系（通用名称）</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>月销量(辆)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>品牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>星愿、派派、龙猫</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>39651</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>吉利牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>星愿、星愿UP</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>39651</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>吉利牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>星愿STAR、星愿</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>39651</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>吉利牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>星愿UP、星愿</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>39651</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>吉利牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>星愿、星愿Ultra</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>39651</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>吉利牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>特斯拉 MODEL Y</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>29260</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>特斯拉牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Model Y</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>29260</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>特斯拉牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>特斯拉 MODEL Y L</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>29260</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>特斯拉(上海)有</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>特斯拉 MODEL3</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>20787</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>特斯拉牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Model 3</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>20787</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>特斯拉牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>特斯拉 MODEL 3</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>20787</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>特斯拉牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>理想i6</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>16979</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>理想牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>海豚</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>16829</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>比亚迪牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>小米SU7</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>16518</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>小米牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>比亚迪宋Ultra,比亚迪大宋</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>15903</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>比亚迪宋Ultra、比亚迪大宋</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>15903</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>比亚迪牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>比亚迪宋Ultra</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>15903</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>比亚迪牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>五菱缤果Pro</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>14695</v>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>五菱牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>比亚迪宋Pro</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>13954</v>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>比亚迪牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>宋PRO</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>13954</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>比亚迪牌</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/NEV公告车型行业分析_数据底表.xlsx
+++ b/NEV公告车型行业分析_数据底表.xlsx
@@ -523,14 +523,14 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>口径版本 v4.9.23 · 5,392 款 × 38 列（第 341~411 批 · 纯乘用车）</t>
+          <t>口径版本 v4.9.23 · 5,392 款 × 39 列（第 341~411 批 · 纯乘用车）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>生成日期 2026-09-30 · 权威源 NEV公告参数汇总表_合并版（341~410批）.xlsx</t>
+          <t>生成日期 2026-10-05 · 权威源 NEV公告参数汇总表_合并版（341~410批）.xlsx</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         <v>64.58</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>33.67</v>
+        <v>33.71</v>
       </c>
     </row>
     <row r="9">
@@ -1052,10 +1052,10 @@
         <v>106</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>89</v>
@@ -1727,10 +1727,10 @@
         <v>93</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>75</v>
@@ -2166,7 +2166,7 @@
         <v>2023</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1862.6</v>
+        <v>1862.4</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>2059.9</v>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="7">
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="8">
@@ -4489,7 +4489,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>249</v>
+        <v>289</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>0</v>
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0</v>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>0</v>
@@ -4558,7 +4558,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>0</v>
@@ -4570,20 +4570,20 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>吉利牌</t>
+          <t>五菱牌</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0</v>
@@ -4592,7 +4592,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>零跑牌</t>
+          <t>东风牌</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
@@ -4602,57 +4602,57 @@
         <v>0</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>东风牌</t>
+          <t>吉利牌</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>五菱牌</t>
+          <t>零跑牌</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
@@ -4748,13 +4748,13 @@
         <v>0</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -4776,7 +4776,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -4795,10 +4795,10 @@
         <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>8</v>
@@ -4807,11 +4807,11 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>吉利牌</t>
+          <t>五菱牌</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>0</v>
@@ -4829,11 +4829,11 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>零跑牌</t>
+          <t>东风牌</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>0</v>
@@ -4851,11 +4851,11 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>东风牌</t>
+          <t>吉利牌</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>0</v>
@@ -4873,11 +4873,11 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>五菱牌</t>
+          <t>零跑牌</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>0</v>
@@ -4895,7 +4895,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏牌</t>
+          <t>哪吒牌</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
@@ -4908,7 +4908,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0</v>
@@ -4917,7 +4917,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>哪吒牌</t>
+          <t>小鹏牌</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
@@ -4930,7 +4930,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0</v>
@@ -6694,13 +6694,13 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>437.7</v>
+        <v>441.5</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>416.9</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>-4.8</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="13">
@@ -6710,13 +6710,13 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>523.5</v>
+        <v>525.5</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>540.1</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -7168,7 +7168,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>2323.3</v>
+        <v>2323.6</v>
       </c>
     </row>
     <row r="15">
@@ -7251,13 +7251,13 @@
         <v>0.576</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.619</v>
+        <v>0.62</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.347</v>
+        <v>0.346</v>
       </c>
     </row>
     <row r="5">
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>0.922</v>
@@ -7332,7 +7332,7 @@
         <v>0.578</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.796</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="8">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.619</v>
+        <v>0.62</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>0.697</v>
@@ -7367,7 +7367,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.347</v>
+        <v>0.346</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>0.678</v>
@@ -7376,7 +7376,7 @@
         <v>0.295</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.796</v>
+        <v>0.797</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>0.446</v>
@@ -7670,7 +7670,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>0.864</v>
+        <v>0.863</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>0.368</v>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.864</v>
+        <v>0.863</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>1</v>
@@ -7925,10 +7925,10 @@
         <v>9.5</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>-1.6</v>
@@ -7997,7 +7997,7 @@
         <v>9.5</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>-3.4</v>
@@ -8150,10 +8150,10 @@
         <v>5.7</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="6">
@@ -8321,7 +8321,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>489.61</v>
+        <v>489.7</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>506</v>
@@ -8369,10 +8369,10 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1823.97</v>
+        <v>1823.94</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>3262</v>
@@ -8476,7 +8476,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>33.07</v>
+        <v>33.08</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>32.7</v>
@@ -8731,7 +8731,7 @@
         <v>2023</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>489.54</v>
+        <v>490.08</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>64.53</v>
@@ -8740,7 +8740,7 @@
         <v>204.7</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>1862.6</v>
+        <v>1862.38</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>33.5</v>
@@ -8819,7 +8819,7 @@
         <v>160.8</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>33.67</v>
+        <v>33.71</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>183.88</v>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>特斯拉(上海)有</t>
+          <t>特斯拉牌</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,11 @@
       <c r="C19" s="5" t="n">
         <v>15903</v>
       </c>
-      <c r="D19" s="5" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>比亚迪牌</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -9772,10 +9776,10 @@
         <v>2023</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>489.54</v>
+        <v>490.08</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>401</v>
@@ -10140,13 +10144,13 @@
         <v>2023</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>489.54</v>
+        <v>490.08</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>116.72</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>372.8</v>
+        <v>373.4</v>
       </c>
     </row>
     <row r="7">
